--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsTrackLogistics.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsTrackLogistics.xlsx
@@ -53,6 +53,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1192,9 +1199,12 @@
       <c r="D2" s="4"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 C2">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
       <formula1>"待下单,已下单,运输中,已到港,已签收"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
+      <formula1>"派送途中,投递失败,成功签收,可能异常,待查询,运输过久,系统完结,查询不到,等待揽收,运输途中,到达待取,手动完结"</formula1>
     </dataValidation>
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>40544</formula1>

--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsTrackLogistics.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsTrackLogistics.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="物流信息" sheetId="1" r:id="rId1"/>
-    <sheet name="费用信息" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <r>
       <rPr>
@@ -119,81 +118,6 @@
   <si>
     <t>轨迹描述</t>
   </si>
-  <si>
-    <t>来源单号</t>
-  </si>
-  <si>
-    <t>物流运单号</t>
-  </si>
-  <si>
-    <t>业务单号</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>费用名称</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>预估费用金额</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>币种</t>
-    </r>
-  </si>
 </sst>
 </file>
 
@@ -215,12 +139,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -375,6 +293,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -713,133 +637,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -847,17 +771,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1170,11 +1094,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="13.3666666666667" customWidth="1"/>
-    <col min="4" max="4" width="21.25" customWidth="1"/>
+    <col min="4" max="4" width="21.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.3666666666667" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1188,15 +1112,12 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="4:4">
-      <c r="D2" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -1215,47 +1136,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
-  <cols>
-    <col min="1" max="5" width="16.0916666666667" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="14.25" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
-      <formula1>0</formula1>
-      <formula2>99999999999999900</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsTrackLogistics.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsTrackLogistics.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="物流信息" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,11 +27,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -41,7 +41,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -53,7 +53,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -63,7 +63,8 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -74,7 +75,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -84,7 +85,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -96,7 +97,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -106,7 +107,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
@@ -117,6 +118,9 @@
   </si>
   <si>
     <t>轨迹描述</t>
+  </si>
+  <si>
+    <t>0000-00-00 00:00:00</t>
   </si>
 </sst>
 </file>
@@ -129,7 +133,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,15 +142,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -295,12 +292,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -496,27 +487,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF1F2329"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF1F2329"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF1F2329"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF1F2329"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -637,151 +613,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -835,7 +802,221 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1094,46 +1275,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="3" width="13.3666666666667" customWidth="1"/>
-    <col min="4" max="4" width="21.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.3666666666667" customWidth="1"/>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="2" width="17.125" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
+    <col min="4" max="4" width="18.125" customWidth="1"/>
+    <col min="5" max="5" width="26.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="4:4">
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
-      <formula1>"待下单,已下单,运输中,已到港,已签收"</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
       <formula1>"派送途中,投递失败,成功签收,可能异常,待查询,运输过久,系统完结,查询不到,等待揽收,运输途中,到达待取,手动完结"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
-      <formula1>40544</formula1>
-      <formula2>47849</formula2>
-    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsTrackLogistics.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsTrackLogistics.xlsx
@@ -743,11 +743,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1281,21 +1287,21 @@
     <col min="1" max="1" width="16.875" customWidth="1"/>
     <col min="2" max="2" width="17.125" customWidth="1"/>
     <col min="3" max="3" width="19.125" customWidth="1"/>
-    <col min="4" max="4" width="18.125" customWidth="1"/>
+    <col min="4" max="4" width="18.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="26.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -1303,7 +1309,7 @@
       </c>
     </row>
     <row r="2" spans="4:4">
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/erp-server/erp-server-tms/src/main/resources/excel/tmsTrackLogistics.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/tmsTrackLogistics.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,49 +27,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>订单号</t>
+  </si>
+  <si>
+    <t>出库单号</t>
+  </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="宋体"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>订单号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>出库单号</t>
+      <t>物流跟踪号</t>
     </r>
   </si>
   <si>
@@ -133,7 +109,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,6 +266,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -743,11 +725,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1281,41 +1266,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="16.875" customWidth="1"/>
-    <col min="2" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="3" width="19.125" customWidth="1"/>
-    <col min="4" max="4" width="18.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5" customWidth="1"/>
+    <col min="1" max="2" width="16.875" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="19.125" customWidth="1"/>
+    <col min="5" max="5" width="18.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="4:4">
-      <c r="D2" s="1" t="s">
-        <v>5</v>
+    <row r="2" spans="5:5">
+      <c r="E2" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576">
       <formula1>"派送途中,投递失败,成功签收,可能异常,待查询,运输过久,系统完结,查询不到,等待揽收,运输途中,到达待取,手动完结"</formula1>
     </dataValidation>
   </dataValidations>
